--- a/Assets/Configs/FoodItem.xlsx
+++ b/Assets/Configs/FoodItem.xlsx
@@ -1,10 +1,10 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet">
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="24750" windowHeight="10480"/>
+    <workbookView windowWidth="22188" windowHeight="10500"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="19" uniqueCount="17">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="40" uniqueCount="28">
   <si>
     <t>ItemID</t>
   </si>
@@ -59,19 +59,52 @@
     <t>Dark</t>
   </si>
   <si>
-    <t>蘑菇</t>
-  </si>
-  <si>
-    <t>食物，食用后会和自然更亲近。</t>
+    <t>西红柿</t>
+  </si>
+  <si>
+    <t>食物，有木属性能量的残留。木属性能量会和自然更亲近。</t>
   </si>
   <si>
     <t>Food</t>
   </si>
   <si>
+    <t>茄子</t>
+  </si>
+  <si>
+    <t>番茄</t>
+  </si>
+  <si>
     <t>狮鹫的肉</t>
   </si>
   <si>
-    <t>食物，上面有风属性能量的残留。</t>
+    <t>食物，有风属性能量的残留。风属性能量会使行动更加迅捷</t>
+  </si>
+  <si>
+    <t>蓝龙的肉</t>
+  </si>
+  <si>
+    <t>食物，有风、水属性能量的残留。风属性能量会使行动更加迅捷，水属性可以提高生命的上限。</t>
+  </si>
+  <si>
+    <t>黑牛的肉</t>
+  </si>
+  <si>
+    <t>食物，有火、水属性能量的残留。火属性能量会使生火能力提高，水属性可以提高生命的上限。</t>
+  </si>
+  <si>
+    <t>棕熊的肉</t>
+  </si>
+  <si>
+    <t>食物，有火属性能量的残留。火属性能量会使生火能力提高。</t>
+  </si>
+  <si>
+    <t>麋鹿的肉</t>
+  </si>
+  <si>
+    <t>马的肉</t>
+  </si>
+  <si>
+    <t>食物，有风、木属性能量的残留。风属性能量会使行动更加迅捷，木属性能量会和自然更亲近。</t>
   </si>
   <si>
     <t>终焉恶魔的肉</t>
@@ -1223,13 +1256,13 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
   <dimension ref="A1:J17"/>
-  <sheetFormatPr defaultColWidth="8.72727272727273" defaultRowHeight="14"/>
+  <sheetFormatPr defaultColWidth="8.73148148148148" defaultRowHeight="14.4"/>
   <cols>
-    <col min="2" max="2" width="13.1818181818182" customWidth="1"/>
-    <col min="3" max="3" width="73.7272727272727" customWidth="1"/>
-    <col min="4" max="5" width="10.7272727272727" customWidth="1"/>
-    <col min="8" max="8" width="10.3636363636364" customWidth="1"/>
-    <col min="9" max="9" width="10.7272727272727" customWidth="1"/>
+    <col min="2" max="2" width="13.1851851851852" customWidth="1"/>
+    <col min="3" max="3" width="96.3333333333333" customWidth="1"/>
+    <col min="4" max="5" width="10.7314814814815" customWidth="1"/>
+    <col min="8" max="8" width="10.3611111111111" customWidth="1"/>
+    <col min="9" max="9" width="10.7314814814815" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:10">
@@ -1304,27 +1337,251 @@
         <v>13</v>
       </c>
       <c r="C3" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="D3">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="E3" t="s">
         <v>12</v>
       </c>
       <c r="F3">
+        <v>0</v>
+      </c>
+      <c r="G3">
+        <v>0</v>
+      </c>
+      <c r="H3">
+        <v>0</v>
+      </c>
+      <c r="I3">
+        <v>5</v>
+      </c>
+      <c r="J3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4" spans="1:10">
+      <c r="A4">
+        <v>2003</v>
+      </c>
+      <c r="B4" t="s">
+        <v>14</v>
+      </c>
+      <c r="C4" t="s">
+        <v>11</v>
+      </c>
+      <c r="D4">
         <v>10</v>
       </c>
-      <c r="G3">
-        <v>0</v>
-      </c>
-      <c r="H3">
-        <v>0</v>
-      </c>
-      <c r="I3">
-        <v>0</v>
-      </c>
-      <c r="J3">
+      <c r="E4" t="s">
+        <v>12</v>
+      </c>
+      <c r="F4">
+        <v>0</v>
+      </c>
+      <c r="G4">
+        <v>0</v>
+      </c>
+      <c r="H4">
+        <v>0</v>
+      </c>
+      <c r="I4">
+        <v>5</v>
+      </c>
+      <c r="J4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5" spans="1:10">
+      <c r="A5">
+        <v>2004</v>
+      </c>
+      <c r="B5" t="s">
+        <v>15</v>
+      </c>
+      <c r="C5" t="s">
+        <v>16</v>
+      </c>
+      <c r="D5">
+        <v>3</v>
+      </c>
+      <c r="E5" t="s">
+        <v>12</v>
+      </c>
+      <c r="F5">
+        <v>8</v>
+      </c>
+      <c r="G5">
+        <v>0</v>
+      </c>
+      <c r="H5">
+        <v>0</v>
+      </c>
+      <c r="I5">
+        <v>0</v>
+      </c>
+      <c r="J5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6" spans="1:10">
+      <c r="A6">
+        <v>2005</v>
+      </c>
+      <c r="B6" t="s">
+        <v>17</v>
+      </c>
+      <c r="C6" t="s">
+        <v>18</v>
+      </c>
+      <c r="D6">
+        <v>3</v>
+      </c>
+      <c r="E6" t="s">
+        <v>12</v>
+      </c>
+      <c r="F6">
+        <v>5</v>
+      </c>
+      <c r="G6">
+        <v>0</v>
+      </c>
+      <c r="H6">
+        <v>3</v>
+      </c>
+      <c r="I6">
+        <v>0</v>
+      </c>
+      <c r="J6">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7" spans="1:10">
+      <c r="A7">
+        <v>2006</v>
+      </c>
+      <c r="B7" t="s">
+        <v>19</v>
+      </c>
+      <c r="C7" t="s">
+        <v>20</v>
+      </c>
+      <c r="D7">
+        <v>3</v>
+      </c>
+      <c r="E7" t="s">
+        <v>12</v>
+      </c>
+      <c r="F7">
+        <v>0</v>
+      </c>
+      <c r="G7">
+        <v>5</v>
+      </c>
+      <c r="H7">
+        <v>3</v>
+      </c>
+      <c r="I7">
+        <v>0</v>
+      </c>
+      <c r="J7">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8" spans="1:10">
+      <c r="A8">
+        <v>2007</v>
+      </c>
+      <c r="B8" t="s">
+        <v>21</v>
+      </c>
+      <c r="C8" t="s">
+        <v>22</v>
+      </c>
+      <c r="D8">
+        <v>3</v>
+      </c>
+      <c r="E8" t="s">
+        <v>12</v>
+      </c>
+      <c r="F8">
+        <v>0</v>
+      </c>
+      <c r="G8">
+        <v>8</v>
+      </c>
+      <c r="H8">
+        <v>0</v>
+      </c>
+      <c r="I8">
+        <v>0</v>
+      </c>
+      <c r="J8">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9" spans="1:10">
+      <c r="A9">
+        <v>2008</v>
+      </c>
+      <c r="B9" t="s">
+        <v>23</v>
+      </c>
+      <c r="C9" t="s">
+        <v>11</v>
+      </c>
+      <c r="D9">
+        <v>3</v>
+      </c>
+      <c r="E9" t="s">
+        <v>12</v>
+      </c>
+      <c r="F9">
+        <v>0</v>
+      </c>
+      <c r="G9">
+        <v>0</v>
+      </c>
+      <c r="H9">
+        <v>0</v>
+      </c>
+      <c r="I9">
+        <v>8</v>
+      </c>
+      <c r="J9">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="10" spans="1:10">
+      <c r="A10">
+        <v>2009</v>
+      </c>
+      <c r="B10" t="s">
+        <v>24</v>
+      </c>
+      <c r="C10" t="s">
+        <v>25</v>
+      </c>
+      <c r="D10">
+        <v>3</v>
+      </c>
+      <c r="E10" t="s">
+        <v>12</v>
+      </c>
+      <c r="F10">
+        <v>3</v>
+      </c>
+      <c r="G10">
+        <v>0</v>
+      </c>
+      <c r="H10">
+        <v>0</v>
+      </c>
+      <c r="I10">
+        <v>5</v>
+      </c>
+      <c r="J10">
         <v>0</v>
       </c>
     </row>
@@ -1333,10 +1590,10 @@
         <v>2345</v>
       </c>
       <c r="B17" t="s">
-        <v>15</v>
+        <v>26</v>
       </c>
       <c r="C17" t="s">
-        <v>16</v>
+        <v>27</v>
       </c>
       <c r="D17">
         <v>1</v>
@@ -1362,7 +1619,7 @@
     </row>
   </sheetData>
   <dataValidations count="1">
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="E$1:E$1048576">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="E4 E1:E3 E5:E1048576">
       <formula1>"Food"</formula1>
     </dataValidation>
   </dataValidations>

--- a/Assets/Configs/FoodItem.xlsx
+++ b/Assets/Configs/FoodItem.xlsx
@@ -1,10 +1,10 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="22188" windowHeight="10500"/>
+    <workbookView windowWidth="24750" windowHeight="10480"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="40" uniqueCount="28">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="41" uniqueCount="29">
   <si>
     <t>ItemID</t>
   </si>
@@ -59,7 +59,10 @@
     <t>Dark</t>
   </si>
   <si>
-    <t>西红柿</t>
+    <t>IsMeat</t>
+  </si>
+  <si>
+    <t>茄子</t>
   </si>
   <si>
     <t>食物，有木属性能量的残留。木属性能量会和自然更亲近。</t>
@@ -68,7 +71,7 @@
     <t>Food</t>
   </si>
   <si>
-    <t>茄子</t>
+    <t>胡萝卜</t>
   </si>
   <si>
     <t>番茄</t>
@@ -1255,17 +1258,17 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:J17"/>
-  <sheetFormatPr defaultColWidth="8.73148148148148" defaultRowHeight="14.4"/>
+  <dimension ref="A1:K17"/>
+  <sheetFormatPr defaultColWidth="8.72727272727273" defaultRowHeight="14"/>
   <cols>
-    <col min="2" max="2" width="13.1851851851852" customWidth="1"/>
-    <col min="3" max="3" width="96.3333333333333" customWidth="1"/>
-    <col min="4" max="5" width="10.7314814814815" customWidth="1"/>
-    <col min="8" max="8" width="10.3611111111111" customWidth="1"/>
-    <col min="9" max="9" width="10.7314814814815" customWidth="1"/>
+    <col min="2" max="2" width="13.1818181818182" customWidth="1"/>
+    <col min="3" max="3" width="96.3363636363636" customWidth="1"/>
+    <col min="4" max="5" width="10.7272727272727" customWidth="1"/>
+    <col min="8" max="8" width="10.3636363636364" customWidth="1"/>
+    <col min="9" max="9" width="10.7272727272727" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10">
+    <row r="1" spans="1:11">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -1296,22 +1299,25 @@
       <c r="J1" t="s">
         <v>9</v>
       </c>
+      <c r="K1" t="s">
+        <v>10</v>
+      </c>
     </row>
-    <row r="2" spans="1:10">
+    <row r="2" spans="1:11">
       <c r="A2">
         <v>2001</v>
       </c>
       <c r="B2" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C2" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="D2">
         <v>10</v>
       </c>
       <c r="E2" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="F2">
         <v>0</v>
@@ -1328,22 +1334,25 @@
       <c r="J2">
         <v>0</v>
       </c>
+      <c r="K2" t="b">
+        <v>0</v>
+      </c>
     </row>
-    <row r="3" spans="1:10">
+    <row r="3" spans="1:11">
       <c r="A3">
         <v>2002</v>
       </c>
       <c r="B3" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="C3" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="D3">
         <v>10</v>
       </c>
       <c r="E3" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="F3">
         <v>0</v>
@@ -1360,22 +1369,25 @@
       <c r="J3">
         <v>0</v>
       </c>
+      <c r="K3" t="b">
+        <v>0</v>
+      </c>
     </row>
-    <row r="4" spans="1:10">
+    <row r="4" spans="1:11">
       <c r="A4">
         <v>2003</v>
       </c>
       <c r="B4" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C4" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="D4">
         <v>10</v>
       </c>
       <c r="E4" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="F4">
         <v>0</v>
@@ -1392,22 +1404,25 @@
       <c r="J4">
         <v>0</v>
       </c>
+      <c r="K4" t="b">
+        <v>0</v>
+      </c>
     </row>
-    <row r="5" spans="1:10">
+    <row r="5" spans="1:11">
       <c r="A5">
         <v>2004</v>
       </c>
       <c r="B5" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C5" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="D5">
         <v>3</v>
       </c>
       <c r="E5" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="F5">
         <v>8</v>
@@ -1424,22 +1439,25 @@
       <c r="J5">
         <v>0</v>
       </c>
+      <c r="K5" t="b">
+        <v>1</v>
+      </c>
     </row>
-    <row r="6" spans="1:10">
+    <row r="6" spans="1:11">
       <c r="A6">
         <v>2005</v>
       </c>
       <c r="B6" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="C6" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="D6">
         <v>3</v>
       </c>
       <c r="E6" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="F6">
         <v>5</v>
@@ -1456,22 +1474,25 @@
       <c r="J6">
         <v>0</v>
       </c>
+      <c r="K6" t="b">
+        <v>1</v>
+      </c>
     </row>
-    <row r="7" spans="1:10">
+    <row r="7" spans="1:11">
       <c r="A7">
         <v>2006</v>
       </c>
       <c r="B7" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="C7" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="D7">
         <v>3</v>
       </c>
       <c r="E7" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="F7">
         <v>0</v>
@@ -1488,22 +1509,25 @@
       <c r="J7">
         <v>0</v>
       </c>
+      <c r="K7" t="b">
+        <v>1</v>
+      </c>
     </row>
-    <row r="8" spans="1:10">
+    <row r="8" spans="1:11">
       <c r="A8">
         <v>2007</v>
       </c>
       <c r="B8" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="C8" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="D8">
         <v>3</v>
       </c>
       <c r="E8" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="F8">
         <v>0</v>
@@ -1520,22 +1544,25 @@
       <c r="J8">
         <v>0</v>
       </c>
+      <c r="K8" t="b">
+        <v>1</v>
+      </c>
     </row>
-    <row r="9" spans="1:10">
+    <row r="9" spans="1:11">
       <c r="A9">
         <v>2008</v>
       </c>
       <c r="B9" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="C9" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="D9">
         <v>3</v>
       </c>
       <c r="E9" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="F9">
         <v>0</v>
@@ -1552,22 +1579,25 @@
       <c r="J9">
         <v>0</v>
       </c>
+      <c r="K9" t="b">
+        <v>1</v>
+      </c>
     </row>
-    <row r="10" spans="1:10">
+    <row r="10" spans="1:11">
       <c r="A10">
         <v>2009</v>
       </c>
       <c r="B10" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="C10" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="D10">
         <v>3</v>
       </c>
       <c r="E10" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="F10">
         <v>3</v>
@@ -1584,22 +1614,25 @@
       <c r="J10">
         <v>0</v>
       </c>
+      <c r="K10" t="b">
+        <v>1</v>
+      </c>
     </row>
-    <row r="17" spans="1:10">
+    <row r="17" spans="1:11">
       <c r="A17">
         <v>2345</v>
       </c>
       <c r="B17" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C17" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="D17">
         <v>1</v>
       </c>
       <c r="E17" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="F17">
         <v>33</v>
@@ -1616,11 +1649,17 @@
       <c r="J17">
         <v>100</v>
       </c>
+      <c r="K17" t="b">
+        <v>1</v>
+      </c>
     </row>
   </sheetData>
-  <dataValidations count="1">
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="E4 E1:E3 E5:E1048576">
+  <dataValidations count="2">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="E3 E1:E2 E4:E1048576">
       <formula1>"Food"</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="K3 K1:K2 K4:K1048576">
+      <formula1>"true,false"</formula1>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/Assets/Configs/FoodItem.xlsx
+++ b/Assets/Configs/FoodItem.xlsx
@@ -1,10 +1,10 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet">
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="24750" windowHeight="10480"/>
+    <workbookView windowWidth="22188" windowHeight="10500"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -83,7 +83,7 @@
     <t>食物，有风属性能量的残留。风属性能量会使行动更加迅捷</t>
   </si>
   <si>
-    <t>蓝龙的肉</t>
+    <t>白熊的肉</t>
   </si>
   <si>
     <t>食物，有风、水属性能量的残留。风属性能量会使行动更加迅捷，水属性可以提高生命的上限。</t>
@@ -1259,13 +1259,13 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
   <dimension ref="A1:K17"/>
-  <sheetFormatPr defaultColWidth="8.72727272727273" defaultRowHeight="14"/>
+  <sheetFormatPr defaultColWidth="8.73148148148148" defaultRowHeight="14.4"/>
   <cols>
-    <col min="2" max="2" width="13.1818181818182" customWidth="1"/>
-    <col min="3" max="3" width="96.3363636363636" customWidth="1"/>
-    <col min="4" max="5" width="10.7272727272727" customWidth="1"/>
-    <col min="8" max="8" width="10.3636363636364" customWidth="1"/>
-    <col min="9" max="9" width="10.7272727272727" customWidth="1"/>
+    <col min="2" max="2" width="13.1851851851852" customWidth="1"/>
+    <col min="3" max="3" width="96.3333333333333" customWidth="1"/>
+    <col min="4" max="5" width="10.7314814814815" customWidth="1"/>
+    <col min="8" max="8" width="10.3611111111111" customWidth="1"/>
+    <col min="9" max="9" width="10.7314814814815" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:11">
@@ -1655,10 +1655,10 @@
     </row>
   </sheetData>
   <dataValidations count="2">
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="E3 E1:E2 E4:E1048576">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="E$1:E$1048576">
       <formula1>"Food"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="K3 K1:K2 K4:K1048576">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="K$1:K$1048576">
       <formula1>"true,false"</formula1>
     </dataValidation>
   </dataValidations>
